--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_firstDrop.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_firstDrop.xlsx
@@ -1,18 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\tszz_TrunkV-5\engine_package\Res\MuDataEditor\生态复古_研发_v1.0.0.0\Out\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="134">
   <si>
     <t>id</t>
   </si>
@@ -103,6 +99,9 @@
     <t>卓越的 紫焰之弓 +幸运 +双卓越</t>
   </si>
   <si>
+    <t>10040001#1600|10040001#960|10040001#320</t>
+  </si>
+  <si>
     <t>卓越的 天魔斗神之铠</t>
   </si>
   <si>
@@ -175,6 +174,9 @@
     <t>卓越的 红羽之弓 +幸运 +双卓越</t>
   </si>
   <si>
+    <t>10040001#1200|10040001#720|10040001#240</t>
+  </si>
+  <si>
     <t>卓越的 魔神之铠</t>
   </si>
   <si>
@@ -205,6 +207,9 @@
     <t>卓越的 幻月雷杖 +幸运 +双卓越</t>
   </si>
   <si>
+    <t>10040001#1000|10040001#600|10040001#200</t>
+  </si>
+  <si>
     <t>卓越的 碧影魔弓</t>
   </si>
   <si>
@@ -253,6 +258,9 @@
     <t>卓越的 追月神弩 +幸运 +双卓越</t>
   </si>
   <si>
+    <t>10040001#800|10040001#480|10040001#160</t>
+  </si>
+  <si>
     <t>卓越的 麒麟之杖</t>
   </si>
   <si>
@@ -277,6 +285,9 @@
     <t>卓越的 圣灵之铠 +幸运 +双卓越</t>
   </si>
   <si>
+    <t>10040001#700|10040001#420|10040001#140</t>
+  </si>
+  <si>
     <t>卓越的 圣灵之弓</t>
   </si>
   <si>
@@ -337,7 +348,7 @@
     <t>卓越的 玄冰剑 +幸运 +双卓越</t>
   </si>
   <si>
-    <t>10040001#1000|10040001#600|10040001#200</t>
+    <t>10040001#500|10040001#300|10040001#100</t>
   </si>
   <si>
     <t>卓越的 温蒂妮</t>
@@ -376,7 +387,7 @@
     <t>卓越的 龙王之铠 +幸运 +双卓越</t>
   </si>
   <si>
-    <t>10040001#800|10040001#480|10040001#160</t>
+    <t>10040001#400|10040001#240|10040001#80</t>
   </si>
   <si>
     <t>卓越的 雷神之剑</t>
@@ -425,28 +436,19 @@
   </si>
   <si>
     <t>卓越的 真红之剑 +幸运 +双卓越</t>
-  </si>
-  <si>
-    <t>10040001#1600|10040001#960|10040001#320</t>
-  </si>
-  <si>
-    <t>10040001#1200|10040001#720|10040001#240</t>
-  </si>
-  <si>
-    <t>10040001#700|10040001#420|10040001#140</t>
-  </si>
-  <si>
-    <t>10040001#500|10040001#300|10040001#100</t>
-  </si>
-  <si>
-    <t>10040001#400|10040001#240|10040001#80</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -458,25 +460,160 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -485,12 +622,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -498,9 +815,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -524,47 +1083,58 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="19">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -578,151 +1148,41 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -733,7 +1193,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -761,40 +1221,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="21"/>
-      <tableStyleElement type="headerRow" dxfId="20"/>
-      <tableStyleElement type="totalRow" dxfId="19"/>
-      <tableStyleElement type="firstColumn" dxfId="18"/>
-      <tableStyleElement type="lastColumn" dxfId="17"/>
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="7"/>
+      <tableStyleElement type="totalRow" dxfId="6"/>
+      <tableStyleElement type="firstColumn" dxfId="5"/>
+      <tableStyleElement type="lastColumn" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" dxfId="3"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="2"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="totalRow" dxfId="17"/>
       <tableStyleElement type="firstRowStripe" dxfId="16"/>
       <tableStyleElement type="firstColumnStripe" dxfId="15"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
-      <tableStyleElement type="headerRow" dxfId="14"/>
-      <tableStyleElement type="totalRow" dxfId="13"/>
-      <tableStyleElement type="firstRowStripe" dxfId="12"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="11"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="10"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="9"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="8"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="7"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="6"/>
-      <tableStyleElement type="pageFieldValues" dxfId="5"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
+      <tableStyleElement type="pageFieldValues" dxfId="9"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1044,14 +1618,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G58"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="18" style="1" customWidth="1"/>
     <col min="2" max="2" width="19.75" style="1" customWidth="1"/>
@@ -1061,7 +1635,7 @@
     <col min="7" max="7" width="61.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1084,7 +1658,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="165" x14ac:dyDescent="0.15">
+    <row r="2" ht="165" spans="1:7">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -1107,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1130,7 +1704,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1153,7 +1727,122 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+  </sheetData>
+  <conditionalFormatting sqref="A$1:A$1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G58"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="18" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="36.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="26.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="61.625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" ht="165" spans="1:7">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="3">
         <v>2013052199</v>
       </c>
@@ -1173,41 +1862,41 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="3">
         <v>1280036699</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="1">
-        <v>3</v>
-      </c>
-      <c r="E6" s="1">
-        <v>2</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="3">
         <v>2012092199</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -1219,18 +1908,18 @@
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="3">
         <v>207699</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
@@ -1242,18 +1931,18 @@
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="3">
         <v>202499</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="1">
         <v>3</v>
@@ -1265,18 +1954,18 @@
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="3">
         <v>202399</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -1288,18 +1977,18 @@
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="3">
         <v>2013102199</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" s="1">
         <v>3</v>
@@ -1311,18 +2000,18 @@
         <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="3">
         <v>2063052199</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" s="1">
         <v>3</v>
@@ -1334,18 +2023,18 @@
         <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="3">
         <v>2062092199</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" s="1">
         <v>3</v>
@@ -1357,18 +2046,18 @@
         <v>1</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="3">
         <v>202199</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
@@ -1380,18 +2069,18 @@
         <v>1</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="3">
         <v>2031072199</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" s="1">
         <v>3</v>
@@ -1403,18 +2092,18 @@
         <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>2061092199</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
@@ -1426,18 +2115,18 @@
         <v>1</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>2013072199</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -1449,41 +2138,41 @@
         <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>1280035699</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="1">
-        <v>3</v>
-      </c>
-      <c r="E18" s="1">
-        <v>2</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>2061072199</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -1495,18 +2184,18 @@
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <v>2062072199</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D20" s="1">
         <v>3</v>
@@ -1518,18 +2207,18 @@
         <v>1</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>202599</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D21" s="1">
         <v>3</v>
@@ -1541,18 +2230,18 @@
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>2012082199</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D22" s="1">
         <v>3</v>
@@ -1564,18 +2253,18 @@
         <v>1</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>2013092199</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D23" s="1">
         <v>3</v>
@@ -1587,41 +2276,41 @@
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>2063072199</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="1">
+        <v>3</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="1">
-        <v>3</v>
-      </c>
-      <c r="E24" s="1">
-        <v>2</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>1280035199</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
@@ -1633,18 +2322,18 @@
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="1">
         <v>1280025199</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D26" s="1">
         <v>3</v>
@@ -1656,18 +2345,18 @@
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="1">
         <v>203199</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D27" s="1">
         <v>3</v>
@@ -1679,18 +2368,18 @@
         <v>1</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>201899</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D28" s="1">
         <v>3</v>
@@ -1702,18 +2391,18 @@
         <v>1</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="1">
         <v>201799</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D29" s="1">
         <v>3</v>
@@ -1725,18 +2414,18 @@
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="1">
         <v>209799</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
@@ -1748,18 +2437,18 @@
         <v>1</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="1">
         <v>2012062199</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -1771,41 +2460,41 @@
         <v>1</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" s="1">
         <v>2061062199</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C32" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" s="1">
+        <v>3</v>
+      </c>
+      <c r="E32" s="1">
+        <v>2</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D32" s="1">
-        <v>3</v>
-      </c>
-      <c r="E32" s="1">
-        <v>2</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="1">
         <v>2031062199</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D33" s="1">
         <v>3</v>
@@ -1817,18 +2506,18 @@
         <v>1</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" s="1">
         <v>2063062199</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D34" s="1">
         <v>3</v>
@@ -1840,18 +2529,18 @@
         <v>1</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="1">
         <v>2013062199</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D35" s="1">
         <v>3</v>
@@ -1863,18 +2552,18 @@
         <v>1</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" s="1">
         <v>207599</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D36" s="1">
         <v>3</v>
@@ -1886,41 +2575,41 @@
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="1">
         <v>2062062199</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" s="1">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2</v>
+      </c>
+      <c r="F37" s="1">
+        <v>1</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D37" s="1">
-        <v>3</v>
-      </c>
-      <c r="E37" s="1">
-        <v>2</v>
-      </c>
-      <c r="F37" s="1">
-        <v>1</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" s="1">
         <v>211999</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D38" s="1">
         <v>3</v>
@@ -1932,18 +2621,18 @@
         <v>1</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" s="1">
         <v>209499</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D39" s="1">
         <v>3</v>
@@ -1955,18 +2644,18 @@
         <v>1</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" s="1">
         <v>2031052199</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D40" s="1">
         <v>3</v>
@@ -1978,18 +2667,18 @@
         <v>1</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" s="1">
         <v>1280034199</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D41" s="1">
         <v>3</v>
@@ -2001,18 +2690,18 @@
         <v>1</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" s="1">
         <v>2062052199</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D42" s="1">
         <v>3</v>
@@ -2024,18 +2713,18 @@
         <v>1</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" s="1">
         <v>226599</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D43" s="1">
         <v>3</v>
@@ -2047,18 +2736,18 @@
         <v>1</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" s="1">
         <v>204999</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D44" s="1">
         <v>3</v>
@@ -2070,18 +2759,18 @@
         <v>1</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" s="1">
         <v>209299</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D45" s="1">
         <v>3</v>
@@ -2093,18 +2782,18 @@
         <v>1</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" s="1">
         <v>2012052199</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D46" s="1">
         <v>3</v>
@@ -2116,41 +2805,41 @@
         <v>1</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" s="1">
         <v>209199</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D47" s="1">
+        <v>3</v>
+      </c>
+      <c r="E47" s="1">
+        <v>2</v>
+      </c>
+      <c r="F47" s="1">
+        <v>1</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D47" s="1">
-        <v>3</v>
-      </c>
-      <c r="E47" s="1">
-        <v>2</v>
-      </c>
-      <c r="F47" s="1">
-        <v>1</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" s="1">
         <v>204899</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D48" s="1">
         <v>3</v>
@@ -2162,18 +2851,18 @@
         <v>1</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" s="1">
         <v>207499</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D49" s="1">
         <v>3</v>
@@ -2185,18 +2874,18 @@
         <v>1</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.15">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" s="1">
         <v>2061042199</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D50" s="1">
         <v>3</v>
@@ -2208,18 +2897,18 @@
         <v>1</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" s="1">
         <v>2031042199</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D51" s="1">
         <v>3</v>
@@ -2231,18 +2920,18 @@
         <v>1</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" s="1">
         <v>2012042199</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D52" s="1">
         <v>3</v>
@@ -2254,41 +2943,41 @@
         <v>1</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" s="1">
         <v>2063042199</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D53" s="1">
+        <v>3</v>
+      </c>
+      <c r="E53" s="1">
+        <v>2</v>
+      </c>
+      <c r="F53" s="1">
+        <v>1</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C53" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D53" s="1">
-        <v>3</v>
-      </c>
-      <c r="E53" s="1">
-        <v>2</v>
-      </c>
-      <c r="F53" s="1">
-        <v>1</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" s="1">
         <v>2013042199</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D54" s="1">
         <v>3</v>
@@ -2300,18 +2989,18 @@
         <v>1</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" s="1">
         <v>201299</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D55" s="1">
         <v>3</v>
@@ -2323,18 +3012,18 @@
         <v>1</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.15">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" s="1">
         <v>2062042199</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D56" s="1">
         <v>3</v>
@@ -2346,18 +3035,18 @@
         <v>1</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" s="1">
         <v>215799</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D57" s="1">
         <v>3</v>
@@ -2369,18 +3058,18 @@
         <v>1</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" s="1">
         <v>2031032199</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D58" s="1">
         <v>3</v>
@@ -2392,22 +3081,22 @@
         <v>1</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+  <conditionalFormatting sqref="A$1:A$1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:A15">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="1" priority="5">
       <formula>AND(SUMPRODUCT(IFERROR(1*(($A$5:$A$15&amp;"x")=(A5&amp;"x")),0))&gt;1,NOT(ISBLANK(A5)))</formula>
     </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>